--- a/data/trans_orig/P3A_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>41362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>668111</t>
+          <t>669746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684578</t>
+          <t>684666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664990</t>
+          <t>664124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679488</t>
+          <t>679905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1340404</t>
+          <t>1339848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1361020</t>
+          <t>1360796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23808</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49566</t>
+          <t>48148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37827</t>
+          <t>36982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67106</t>
+          <t>67842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>912234</t>
+          <t>913652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>937992</t>
+          <t>937433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>942983</t>
+          <t>943041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959041</t>
+          <t>959490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1863087</t>
+          <t>1862351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1892366</t>
+          <t>1893211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>15804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36235</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>35683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>63868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642274</t>
+          <t>641836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661936</t>
+          <t>662705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645932</t>
+          <t>646258</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665646</t>
+          <t>666467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1296396</t>
+          <t>1295084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324137</t>
+          <t>1323269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42795</t>
+          <t>43531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74042</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40583</t>
+          <t>40296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68956</t>
+          <t>69758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91378</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130911</t>
+          <t>131844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867298</t>
+          <t>868606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>898545</t>
+          <t>897809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>969656</t>
+          <t>968854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>998029</t>
+          <t>998316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1849041</t>
+          <t>1848108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1888574</t>
+          <t>1887121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110225</t>
+          <t>111528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156128</t>
+          <t>161196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87566</t>
+          <t>86206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128710</t>
+          <t>126266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211408</t>
+          <t>209386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271328</t>
+          <t>269777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3119533</t>
+          <t>3114465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3165436</t>
+          <t>3164133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3245935</t>
+          <t>3248379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3287079</t>
+          <t>3288439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6378979</t>
+          <t>6380530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6438899</t>
+          <t>6440921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>41881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>40924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>74972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661091</t>
+          <t>661588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682690</t>
+          <t>681119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>656535</t>
+          <t>656126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>678596</t>
+          <t>678632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1325066</t>
+          <t>1325547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1356134</t>
+          <t>1356183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30240</t>
+          <t>30464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57342</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57065</t>
+          <t>56847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65997</t>
+          <t>65218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104573</t>
+          <t>103831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>959546</t>
+          <t>958195</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>986648</t>
+          <t>986424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>975119</t>
+          <t>975337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1002549</t>
+          <t>1002583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1944499</t>
+          <t>1945241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1983075</t>
+          <t>1983854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32376</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62876</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>730617</t>
+          <t>729515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>748460</t>
+          <t>748671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>733520</t>
+          <t>734547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>757503</t>
+          <t>757125</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1469920</t>
+          <t>1470605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1500420</t>
+          <t>1500583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30790</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56072</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48880</t>
+          <t>48793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81909</t>
+          <t>80473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84780</t>
+          <t>87928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125211</t>
+          <t>128177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891667</t>
+          <t>891497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916949</t>
+          <t>917562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>969992</t>
+          <t>971428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003021</t>
+          <t>1003108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874429</t>
+          <t>1871463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914860</t>
+          <t>1911712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>107120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154617</t>
+          <t>156295</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139713</t>
+          <t>135629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192863</t>
+          <t>188487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>260008</t>
+          <t>261714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>327290</t>
+          <t>328811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3271102</t>
+          <t>3269424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3317986</t>
+          <t>3318599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3363445</t>
+          <t>3367821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3416595</t>
+          <t>3420679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6654737</t>
+          <t>6653216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6722019</t>
+          <t>6720313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46678</t>
+          <t>45881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653202</t>
+          <t>652575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667135</t>
+          <t>667317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641706</t>
+          <t>641166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660884</t>
+          <t>661091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1300027</t>
+          <t>1300824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1324250</t>
+          <t>1324870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>988252</t>
+          <t>989785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1007812</t>
+          <t>1007736</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1003368</t>
+          <t>1001896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025987</t>
+          <t>1026012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1999460</t>
+          <t>2000063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2029034</t>
+          <t>2028804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>24620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51083</t>
+          <t>52146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726991</t>
+          <t>727423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>745345</t>
+          <t>745749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>752044</t>
+          <t>752517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>771322</t>
+          <t>771593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1487585</t>
+          <t>1486522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1512831</t>
+          <t>1514048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>42704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58336</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56650</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>92132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891142</t>
+          <t>890658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>912411</t>
+          <t>912185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>984402</t>
+          <t>984331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1012353</t>
+          <t>1011999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1884926</t>
+          <t>1883968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1919450</t>
+          <t>1921500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66300</t>
+          <t>64369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101792</t>
+          <t>100996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>87941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>132776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162745</t>
+          <t>158996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>220265</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3283517</t>
+          <t>3284313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3319009</t>
+          <t>3320940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3407457</t>
+          <t>3406804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3454645</t>
+          <t>3451639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6704625</t>
+          <t>6706099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6762145</t>
+          <t>6765894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>30660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>51967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57186</t>
+          <t>57806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73307</t>
+          <t>73002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102437</t>
+          <t>102025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>582862</t>
+          <t>583008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604397</t>
+          <t>604315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>668144</t>
+          <t>667524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688987</t>
+          <t>689152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1257868</t>
+          <t>1258280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1286998</t>
+          <t>1287303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53347</t>
+          <t>53063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40087</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>60914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58873</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107001</t>
+          <t>104993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1139517</t>
+          <t>1139801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1176402</t>
+          <t>1175415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>897377</t>
+          <t>897737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>918564</t>
+          <t>919023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2044515</t>
+          <t>2046523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2092643</t>
+          <t>2094419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>17834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>37817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>48412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40163</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79310</t>
+          <t>78267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665957</t>
+          <t>666863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>686422</t>
+          <t>686846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>882635</t>
+          <t>884954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>915684</t>
+          <t>918327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1558736</t>
+          <t>1559779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1597883</t>
+          <t>1598149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35956</t>
+          <t>35787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62441</t>
+          <t>61263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52277</t>
+          <t>51868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81205</t>
+          <t>81020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95220</t>
+          <t>95519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133396</t>
+          <t>134694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>863758</t>
+          <t>864936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>890243</t>
+          <t>890412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1012468</t>
+          <t>1012653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1041396</t>
+          <t>1041805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886475</t>
+          <t>1885177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1924651</t>
+          <t>1924352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115754</t>
+          <t>115599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179417</t>
+          <t>174998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165465</t>
+          <t>157053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223279</t>
+          <t>225152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>303718</t>
+          <t>299741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390597</t>
+          <t>389766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3279301</t>
+          <t>3283720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3342964</t>
+          <t>3343119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3487741</t>
+          <t>3485868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3545555</t>
+          <t>3553967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6779141</t>
+          <t>6779972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6866020</t>
+          <t>6869997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41362</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669746</t>
+          <t>669827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684666</t>
+          <t>684423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664124</t>
+          <t>664767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679905</t>
+          <t>679412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1339848</t>
+          <t>1339372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1360796</t>
+          <t>1360615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>48196</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36982</t>
+          <t>37931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67842</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>913652</t>
+          <t>913604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>937433</t>
+          <t>937362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>943041</t>
+          <t>943165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959490</t>
+          <t>959733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1862351</t>
+          <t>1862270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1893211</t>
+          <t>1892262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>35921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>14978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34185</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>35529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63868</t>
+          <t>63091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641836</t>
+          <t>642588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662705</t>
+          <t>661851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646258</t>
+          <t>646515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666467</t>
+          <t>665465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1295084</t>
+          <t>1295861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323269</t>
+          <t>1323423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43531</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72734</t>
+          <t>74328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40296</t>
+          <t>39806</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69758</t>
+          <t>68999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>91603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131844</t>
+          <t>131904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>868606</t>
+          <t>867012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>897809</t>
+          <t>897669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968854</t>
+          <t>969613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>998316</t>
+          <t>998806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848108</t>
+          <t>1848048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1887121</t>
+          <t>1888349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111528</t>
+          <t>111755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161196</t>
+          <t>157176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>86834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126266</t>
+          <t>128260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209386</t>
+          <t>211271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269777</t>
+          <t>270028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3114465</t>
+          <t>3118485</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3164133</t>
+          <t>3163906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3248379</t>
+          <t>3246385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3288439</t>
+          <t>3287811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6380530</t>
+          <t>6380279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6440921</t>
+          <t>6439036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41881</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40924</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44336</t>
+          <t>45036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74972</t>
+          <t>74547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661588</t>
+          <t>661561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>681119</t>
+          <t>682672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>656126</t>
+          <t>657286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>678632</t>
+          <t>677697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1325547</t>
+          <t>1325972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1356183</t>
+          <t>1355483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30464</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>57973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56847</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65218</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103831</t>
+          <t>104239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>958195</t>
+          <t>958915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>986424</t>
+          <t>986108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>975337</t>
+          <t>975277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1002583</t>
+          <t>1001716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1945241</t>
+          <t>1944833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1983854</t>
+          <t>1980982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28108</t>
+          <t>27124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>42159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>32576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62191</t>
+          <t>63526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>729515</t>
+          <t>730499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>748671</t>
+          <t>748770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>734547</t>
+          <t>733014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>757125</t>
+          <t>755523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1470605</t>
+          <t>1469270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1500583</t>
+          <t>1500220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48793</t>
+          <t>48332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80473</t>
+          <t>83048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87928</t>
+          <t>84659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128177</t>
+          <t>125525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891497</t>
+          <t>891627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917562</t>
+          <t>917989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971428</t>
+          <t>968853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003108</t>
+          <t>1003569</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1871463</t>
+          <t>1874115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1911712</t>
+          <t>1914981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107120</t>
+          <t>106620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156295</t>
+          <t>154326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135629</t>
+          <t>135337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188487</t>
+          <t>187871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>261714</t>
+          <t>256649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>328811</t>
+          <t>329203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3269424</t>
+          <t>3271393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3318599</t>
+          <t>3319099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3367821</t>
+          <t>3368437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3420679</t>
+          <t>3420971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6653216</t>
+          <t>6652824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6720313</t>
+          <t>6725378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30739</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45881</t>
+          <t>46270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652575</t>
+          <t>652807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667317</t>
+          <t>667366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641166</t>
+          <t>640980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661091</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1300824</t>
+          <t>1300435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1324870</t>
+          <t>1325415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40063</t>
+          <t>41299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63354</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>989785</t>
+          <t>986505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1007736</t>
+          <t>1007433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1001896</t>
+          <t>1000660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1026012</t>
+          <t>1025769</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2000063</t>
+          <t>1999241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028804</t>
+          <t>2028979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>27737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>31164</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>26389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52146</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>727423</t>
+          <t>727952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>745749</t>
+          <t>745675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>752517</t>
+          <t>751815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>771593</t>
+          <t>771653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1486522</t>
+          <t>1486047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1514048</t>
+          <t>1512279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21177</t>
+          <t>20746</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42704</t>
+          <t>41479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30739</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58407</t>
+          <t>57255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54600</t>
+          <t>56356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92132</t>
+          <t>93285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890658</t>
+          <t>891883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>912185</t>
+          <t>912616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>984331</t>
+          <t>985483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1011999</t>
+          <t>1013685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1883968</t>
+          <t>1882815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1921500</t>
+          <t>1919744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>66300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100996</t>
+          <t>100802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87941</t>
+          <t>87896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132776</t>
+          <t>132928</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158996</t>
+          <t>162606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>218791</t>
+          <t>221779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3284313</t>
+          <t>3284507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3320940</t>
+          <t>3319009</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3406804</t>
+          <t>3406652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3451639</t>
+          <t>3451684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6706099</t>
+          <t>6703111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6765894</t>
+          <t>6762284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>32038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51967</t>
+          <t>54155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47512</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36178</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57806</t>
+          <t>61272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>87518</t>
+          <t>93525</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73002</t>
+          <t>79526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102025</t>
+          <t>109724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>594969</t>
+          <t>648346</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>583008</t>
+          <t>636071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604315</t>
+          <t>658188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>677818</t>
+          <t>682534</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667524</t>
+          <t>672908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689152</t>
+          <t>692241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1272787</t>
+          <t>1330881</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1258280</t>
+          <t>1314682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1287303</t>
+          <t>1344880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35255</t>
+          <t>39594</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53063</t>
+          <t>58077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>66405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>84639</t>
+          <t>93643</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57097</t>
+          <t>77336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104993</t>
+          <t>113393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1157609</t>
+          <t>1009323</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1139801</t>
+          <t>990840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1175415</t>
+          <t>1021419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>909266</t>
+          <t>1017425</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>897737</t>
+          <t>1005069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>919023</t>
+          <t>1027289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2066877</t>
+          <t>2026748</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2046523</t>
+          <t>2006998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2094419</t>
+          <t>2043055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26717</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35001</t>
+          <t>40320</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>71591</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>58472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>88880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>677963</t>
+          <t>771802</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666863</t>
+          <t>758493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>686846</t>
+          <t>782169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>898365</t>
+          <t>771939</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>884954</t>
+          <t>760945</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>918327</t>
+          <t>781280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1576327</t>
+          <t>1543741</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1559779</t>
+          <t>1526452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1598149</t>
+          <t>1556860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47072</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>37243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61263</t>
+          <t>64833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>60731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81020</t>
+          <t>86906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113903</t>
+          <t>121018</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95519</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134694</t>
+          <t>141122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879127</t>
+          <t>940777</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>864936</t>
+          <t>924619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>890412</t>
+          <t>952209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1026841</t>
+          <t>1045453</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1012653</t>
+          <t>1030890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1041805</t>
+          <t>1057065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1905968</t>
+          <t>1986231</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885177</t>
+          <t>1966127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1924352</t>
+          <t>2003429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>149050</t>
+          <t>161420</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115599</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174998</t>
+          <t>189508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>198729</t>
+          <t>218358</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157053</t>
+          <t>195052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>225152</t>
+          <t>241052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>347779</t>
+          <t>379778</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299741</t>
+          <t>346329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>389766</t>
+          <t>416088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3309668</t>
+          <t>3370249</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3283720</t>
+          <t>3342161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3343119</t>
+          <t>3392609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3512291</t>
+          <t>3517351</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3485868</t>
+          <t>3494657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3553967</t>
+          <t>3540657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6821959</t>
+          <t>6887600</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6779972</t>
+          <t>6851290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6869997</t>
+          <t>6921049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
